--- a/docs/design/ACSMS-SCR-012/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_パスワードの再設定・パスワードの変更_V1.1.xlsx
+++ b/docs/design/ACSMS-SCR-012/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_パスワードの再設定・パスワードの変更_V1.1.xlsx
@@ -1722,7 +1722,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -1730,7 +1730,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1738,7 +1738,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -1995,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2148,7 +2148,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2156,7 +2156,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2164,7 +2164,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -2390,7 +2390,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>INTERNAL_SERVER_ERROR</t>
+          <t>TOO_MANY_REQUESTS</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -2406,7 +2406,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="19" t="inlineStr">
         <is>
-          <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
+          <t>リクエスト回数が上限を超えました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
       <c r="W8" s="10" t="n"/>
@@ -2432,7 +2432,7 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>画面固有</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -2443,7 +2443,7 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>INVALID_RESET_TOKEN</t>
+          <t>INTERNAL_SERVER_ERROR</t>
         </is>
       </c>
       <c r="K9" s="10" t="n"/>
@@ -2459,7 +2459,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="19" t="inlineStr">
         <is>
-          <t>無効なリンクです。</t>
+          <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
       <c r="W9" s="10" t="n"/>
@@ -2496,7 +2496,7 @@
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>EXPIRED_RESET_TOKEN</t>
+          <t>INVALID_RESET_TOKEN</t>
         </is>
       </c>
       <c r="K10" s="10" t="n"/>
@@ -2512,7 +2512,7 @@
       <c r="U10" s="11" t="n"/>
       <c r="V10" s="19" t="inlineStr">
         <is>
-          <t>リンクの有効期限が切れています。再度パスワード再設定をお試しください。</t>
+          <t>無効なリンクです。</t>
         </is>
       </c>
       <c r="W10" s="10" t="n"/>
@@ -2549,7 +2549,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>PASSWORD_RESET_RATE_LIMIT</t>
+          <t>EXPIRED_RESET_TOKEN</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -2565,7 +2565,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="19" t="inlineStr">
         <is>
-          <t>再送信は5分後に可能です。時間をおいてから再度お試しください。</t>
+          <t>リンクの有効期限が切れています。再度パスワード再設定をお試しください。</t>
         </is>
       </c>
       <c r="W11" s="10" t="n"/>
@@ -2584,8 +2584,61 @@
       <c r="AJ11" s="10" t="n"/>
       <c r="AK11" s="11" t="n"/>
     </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>PASSWORD_RESET_RATE_LIMIT</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="11" t="n"/>
+      <c r="V12" s="19" t="inlineStr">
+        <is>
+          <t>再送信は5分後に可能です。時間をおいてから再度お試しください。</t>
+        </is>
+      </c>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
+      <c r="AB12" s="10" t="n"/>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="10" t="n"/>
+      <c r="AH12" s="10" t="n"/>
+      <c r="AI12" s="10" t="n"/>
+      <c r="AJ12" s="10" t="n"/>
+      <c r="AK12" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="46">
     <mergeCell ref="V11:AK11"/>
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
@@ -2600,11 +2653,14 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C6:I6"/>
+    <mergeCell ref="V12:AK12"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="C5:I5"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="J12:U12"/>
     <mergeCell ref="V5:AK5"/>
     <mergeCell ref="V8:AK8"/>
     <mergeCell ref="Q1:U1"/>
@@ -2624,6 +2680,7 @@
     <mergeCell ref="V9:AK9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C12:I12"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="V6:AK6"/>
     <mergeCell ref="C11:I11"/>
@@ -2792,7 +2849,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -2800,7 +2857,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2808,7 +2865,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3290,7 +3347,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -3298,7 +3355,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3306,7 +3363,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -5023,10 +5080,10 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
+    <row r="96" ht="54" customHeight="1">
       <c r="D96" s="39" t="inlineStr">
         <is>
-          <t>HTTP 500 を返す（トークンは削除）</t>
+          <t>HTTP 500 を返す。トークンはDBトランザクションのcommit後に送信するため、送信失敗時もDB上のトークン行は削除・ロールバックされず有効期限内は有効なまま残る（例外は catch されず GlobalExceptionFilter が 500 に整形する）</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5418,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -5369,7 +5426,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5377,7 +5434,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -6535,19 +6592,20 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="54" customHeight="1">
       <c r="C55" s="39" t="inlineStr">
         <is>
-          <t>以下の条件でトークンを検索する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="54" customHeight="1">
+          <t>以下の条件でトークンを検索する（`used_flg = false` の行のみが候補。bcryptハッシュのため直接WHERE一致はできず、候補行を取得して`token`と`otp_code_hash`を1件ずつ`bcrypt.compare`する）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="72" customHeight="1">
       <c r="C56" s="38" t="inlineStr">
         <is>
           <t>SELECT otp_id, account_id, expired_at, used_flg
 FROM t_mfa_otp
-WHERE otp_type = 2</t>
+WHERE otp_type = 2
+  AND used_flg = false</t>
         </is>
       </c>
       <c r="D56" s="10" t="n"/>
@@ -6585,10 +6643,10 @@
       <c r="AJ56" s="10" t="n"/>
       <c r="AK56" s="11" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="36" customHeight="1">
       <c r="C57" s="39" t="inlineStr">
         <is>
-          <t>トークンが見つからない場合：</t>
+          <t>トークンが見つからない場合（使用済みトークンも検索条件から除外されるため「見つからない」扱いになる。4.5 は結果的に到達しない）：</t>
         </is>
       </c>
     </row>
@@ -6966,7 +7024,7 @@
       <c r="Y2" s="22" t="n"/>
       <c r="Z2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AA2" s="21" t="n"/>
@@ -6974,7 +7032,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/12</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6982,7 +7040,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Nguyen Truong An</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -8378,19 +8436,20 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67" ht="72" customHeight="1">
       <c r="C67" s="39" t="inlineStr">
         <is>
-          <t>以下の条件でトークンを検索する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="54" customHeight="1">
+          <t>以下の条件でトークンを検索する（`used_flg = false` の行のみが候補。bcryptハッシュのため直接WHERE一致はできず、候補行を取得して`token`と`otp_code_hash`を1件ずつ`bcrypt.compare`する。ACSMS-API-012-002と同一の検索ロジックを再利用）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="72" customHeight="1">
       <c r="C68" s="38" t="inlineStr">
         <is>
           <t>SELECT otp_id, account_id, expired_at, used_flg, otp_code_hash
 FROM t_mfa_otp
-WHERE otp_type = 2</t>
+WHERE otp_type = 2
+  AND used_flg = false</t>
         </is>
       </c>
       <c r="D68" s="10" t="n"/>
